--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,113 +887,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>129432975</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79043</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Hålklappberget, Hålklappberget, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>793724</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7146007</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Nysätra</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129432977</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129432977</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129432977</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129433359</v>
       </c>
       <c r="B3" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>130142367</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>130142367</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>130142367</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44084-2025 artfynd.xlsx
+++ b/artfynd/A 44084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129433359</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142367</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129432977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>